--- a/Best_MAIT_markers.xlsx
+++ b/Best_MAIT_markers.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
   <si>
     <t xml:space="preserve">p_val</t>
   </si>
@@ -38,256 +38,316 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
+    <t xml:space="preserve">CCL20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IL4I1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TNF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTRNR2L8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AQP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NCR3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERPINB9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LTB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IER5L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCR6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRAV1-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IL23R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPR171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUBB2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IL7R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNAJB9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDKN1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CST3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HLA-DRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HLA-DRB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HLA-DPB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HLA-DPA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL138963.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMSN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL627171.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIST1H1E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOMER1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZEB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZHX2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIPA1L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TNFRSF1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHNAK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZSWIM6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL031599.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XCL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPRY2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOX2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FCER1G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NCR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XCL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTPRD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCL3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KLRC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B3GNT7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LZTFL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCBTB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLFN13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIC3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KLRC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP8B4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
     <t xml:space="preserve">CISH</t>
   </si>
   <si>
-    <t xml:space="preserve">AC004832.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNAI1</t>
-  </si>
-  <si>
     <t xml:space="preserve">CD40LG</t>
   </si>
   <si>
-    <t xml:space="preserve">JUN</t>
+    <t xml:space="preserve">ZNF22</t>
   </si>
   <si>
     <t xml:space="preserve">PIM1</t>
   </si>
   <si>
-    <t xml:space="preserve">AL499604.1</t>
+    <t xml:space="preserve">GIMAP7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIMAP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RORC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARL14EP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLT3LG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIMAP4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRAP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRAF3IP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTIF3</t>
   </si>
   <si>
     <t xml:space="preserve">ANXA2R</t>
   </si>
   <si>
-    <t xml:space="preserve">GIMAP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCART1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLAMF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIRPG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IER3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSPAN15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RGS19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLT3LG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEX14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RORC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCL20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIM3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AQP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NINJ1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LMNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RGCC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CXCR4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPR183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPR65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERPINB9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PBX4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MT2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FURIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRDX1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLK3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCR6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRNP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BACH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
+    <t xml:space="preserve">CHURC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC006369.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LINC01871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FGFBP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKR1C3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYOM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CX3CR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADGRG1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GZMB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNLY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FCGR3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTSS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPON2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRSS23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAVCR2</t>
   </si>
   <si>
     <t xml:space="preserve">SH2D1B</t>
   </si>
   <si>
-    <t xml:space="preserve">AL031599.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B3GNT7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FCER1G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NCR1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOX2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPRY2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XCL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XCL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SYK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIC3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTPRD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KLRC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KLRC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRDC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FGR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3MBTL4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TYROBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CST3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HLA-DRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HLA-DRB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HLA-DPB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HLA-DPA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZEB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL138963.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RASA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IQCN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HBB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LGALS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDE3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNLY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOMER1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HIST1H1E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL627171.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TNFRSF1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P2RY8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZHX2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
+    <t xml:space="preserve">RAP1GAP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSBPL5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BNC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTC38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
   </si>
   <si>
     <t xml:space="preserve">AC004448.2</t>
@@ -299,118 +359,118 @@
     <t xml:space="preserve">FP236383.3</t>
   </si>
   <si>
+    <t xml:space="preserve">AC138123.1</t>
+  </si>
+  <si>
     <t xml:space="preserve">RBFOX2</t>
   </si>
   <si>
-    <t xml:space="preserve">AC138123.1</t>
-  </si>
-  <si>
     <t xml:space="preserve">APOO</t>
   </si>
   <si>
+    <t xml:space="preserve">RPS10-NUDT3</t>
+  </si>
+  <si>
     <t xml:space="preserve">FP671120.4</t>
   </si>
   <si>
-    <t xml:space="preserve">RPS10-NUDT3</t>
-  </si>
-  <si>
     <t xml:space="preserve">U2AF1L5</t>
   </si>
   <si>
     <t xml:space="preserve">OOEP</t>
   </si>
   <si>
+    <t xml:space="preserve">PTPRCAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC105402.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FKBP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRBV6-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNLRB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAA10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATR3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYVN1</t>
+  </si>
+  <si>
     <t xml:space="preserve">GZMH</t>
   </si>
   <si>
-    <t xml:space="preserve">PTPRCAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLEKHA7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FKBP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SYVN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAA10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRBV6-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MATR3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNLRB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LINC01524</t>
+    <t xml:space="preserve">TRIM69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
   </si>
   <si>
     <t xml:space="preserve">NR3C2</t>
   </si>
   <si>
+    <t xml:space="preserve">LINC02694</t>
+  </si>
+  <si>
     <t xml:space="preserve">PCAT1</t>
   </si>
   <si>
-    <t xml:space="preserve">LINC02694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADCY9</t>
+    <t xml:space="preserve">ARHGAP10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL136456.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC093865.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XIST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TANGO6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANK3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFF3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPON1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIAM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCL2</t>
   </si>
   <si>
     <t xml:space="preserve">WWOX</t>
   </si>
   <si>
-    <t xml:space="preserve">TIAM2</t>
+    <t xml:space="preserve">LINC01644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCFD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRADD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGAP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAM19</t>
   </si>
   <si>
     <t xml:space="preserve">C22orf34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPON1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMCC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL136456.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC9A9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIPR1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XIST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTPRM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BBS9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGAP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INPP5A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AOPEP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC008014.1</t>
   </si>
 </sst>
 </file>
@@ -764,19 +824,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0000000000000000000000000000000000000000000951069471252885</v>
+        <v>0.000000000000000000000000000000000000000364634660707167</v>
       </c>
       <c r="B2" t="n">
-        <v>3.20248632051972</v>
+        <v>2.92092115768402</v>
       </c>
       <c r="C2" t="n">
-        <v>0.317</v>
+        <v>0.307</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05</v>
+        <v>0.087</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00000000000000000000000000000000000000348100937173269</v>
+        <v>0.000000000000000000000000000000000013345993216543</v>
       </c>
       <c r="F2" t="s">
         <v>7</v>
@@ -787,19 +847,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.0000000000000000000000000000000116465717819212</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000014326473931959</v>
       </c>
       <c r="B3" t="n">
-        <v>2.96945275118471</v>
+        <v>1.94844865054525</v>
       </c>
       <c r="C3" t="n">
-        <v>0.258</v>
+        <v>0.582</v>
       </c>
       <c r="D3" t="n">
-        <v>0.044</v>
+        <v>0.148</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000000000000000000000000000426276173790099</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000524363272383631</v>
       </c>
       <c r="F3" t="s">
         <v>7</v>
@@ -810,19 +870,19 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.00000000000000000000000613325720316093</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000478272305746692</v>
       </c>
       <c r="B4" t="n">
-        <v>2.37839479856796</v>
+        <v>1.82602789851892</v>
       </c>
       <c r="C4" t="n">
-        <v>0.274</v>
+        <v>0.511</v>
       </c>
       <c r="D4" t="n">
-        <v>0.077</v>
+        <v>0.165</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000000000000000000224483346892893</v>
+        <v>0.00000000000000000000000000000000000000000000000000000175052446626347</v>
       </c>
       <c r="F4" t="s">
         <v>7</v>
@@ -833,19 +893,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.000000000000000000000000000000000000000000000342410363449284</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000458098095333299</v>
       </c>
       <c r="B5" t="n">
-        <v>2.12771904804556</v>
+        <v>1.78120471204835</v>
       </c>
       <c r="C5" t="n">
-        <v>0.443</v>
+        <v>0.769</v>
       </c>
       <c r="D5" t="n">
-        <v>0.115</v>
+        <v>0.3</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0000000000000000000000000000000000000000125325617126072</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000167668483872941</v>
       </c>
       <c r="F5" t="s">
         <v>7</v>
@@ -856,19 +916,19 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.000000000000000000000000000000000000000000707124196029332</v>
+        <v>0.000000000000000000000000000000834642889750212</v>
       </c>
       <c r="B6" t="n">
-        <v>1.86393832842905</v>
+        <v>1.71520936363915</v>
       </c>
       <c r="C6" t="n">
-        <v>0.824</v>
+        <v>0.348</v>
       </c>
       <c r="D6" t="n">
-        <v>0.543</v>
+        <v>0.143</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0000000000000000000000000000000000000258814526988696</v>
+        <v>0.0000000000000000000000000305487644077475</v>
       </c>
       <c r="F6" t="s">
         <v>7</v>
@@ -879,19 +939,19 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0000000000000000000000000000000151668154204919</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000101887954919321</v>
       </c>
       <c r="B7" t="n">
-        <v>1.67157106135019</v>
+        <v>1.71017679100803</v>
       </c>
       <c r="C7" t="n">
-        <v>0.47</v>
+        <v>0.717</v>
       </c>
       <c r="D7" t="n">
-        <v>0.18</v>
+        <v>0.232</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000000000000000000000000000555120611205424</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000372920103800208</v>
       </c>
       <c r="F7" t="s">
         <v>7</v>
@@ -902,19 +962,19 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.00000000000000000381076813770238</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000125438152692293</v>
       </c>
       <c r="B8" t="n">
-        <v>1.63491826006936</v>
+        <v>1.53797033054713</v>
       </c>
       <c r="C8" t="n">
-        <v>0.288</v>
+        <v>0.787</v>
       </c>
       <c r="D8" t="n">
-        <v>0.108</v>
+        <v>0.323</v>
       </c>
       <c r="E8" t="n">
-        <v>0.000000000000139477924608045</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000459116182669063</v>
       </c>
       <c r="F8" t="s">
         <v>7</v>
@@ -925,19 +985,19 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.0000000000000000000198679779064444</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000138813650542022</v>
       </c>
       <c r="B9" t="n">
-        <v>1.62559952467068</v>
+        <v>1.5206881146629</v>
       </c>
       <c r="C9" t="n">
-        <v>0.315</v>
+        <v>0.603</v>
       </c>
       <c r="D9" t="n">
-        <v>0.115</v>
+        <v>0.204</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00000000000000072718785935377</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000508071842348855</v>
       </c>
       <c r="F9" t="s">
         <v>7</v>
@@ -948,19 +1008,19 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.000000000000000000000000000000000000162843966094682</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000212682274637921</v>
       </c>
       <c r="B10" t="n">
-        <v>1.61938622515713</v>
+        <v>1.44680769525287</v>
       </c>
       <c r="C10" t="n">
-        <v>0.498</v>
+        <v>0.964</v>
       </c>
       <c r="D10" t="n">
-        <v>0.174</v>
+        <v>0.445</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00000000000000000000000000000000596025200303147</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000778438393402253</v>
       </c>
       <c r="F10" t="s">
         <v>7</v>
@@ -971,19 +1031,19 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0000000000000474437222552788</v>
+        <v>0.000000000000000000000000000000000000000000000593611953814281</v>
       </c>
       <c r="B11" t="n">
-        <v>1.42701459046516</v>
+        <v>1.40146143491102</v>
       </c>
       <c r="C11" t="n">
-        <v>0.274</v>
+        <v>0.417</v>
       </c>
       <c r="D11" t="n">
-        <v>0.117</v>
+        <v>0.131</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00000000173648767826546</v>
+        <v>0.0000000000000000000000000000000000000000217267911215565</v>
       </c>
       <c r="F11" t="s">
         <v>7</v>
@@ -994,19 +1054,19 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0000000000000000000000000374020817579522</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000263856283769106</v>
       </c>
       <c r="B12" t="n">
-        <v>1.39635351953175</v>
+        <v>1.34698015210573</v>
       </c>
       <c r="C12" t="n">
-        <v>0.413</v>
+        <v>0.578</v>
       </c>
       <c r="D12" t="n">
-        <v>0.158</v>
+        <v>0.189</v>
       </c>
       <c r="E12" t="n">
-        <v>0.00000000000000000000136895359442281</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000965740384223304</v>
       </c>
       <c r="F12" t="s">
         <v>7</v>
@@ -1017,19 +1077,19 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.00000000000000000123498540788308</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000940161388657482</v>
       </c>
       <c r="B13" t="n">
-        <v>1.39414223055574</v>
+        <v>1.28710452437295</v>
       </c>
       <c r="C13" t="n">
-        <v>0.347</v>
+        <v>0.787</v>
       </c>
       <c r="D13" t="n">
-        <v>0.147</v>
+        <v>0.291</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0000000000000452017009139287</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000344108469862525</v>
       </c>
       <c r="F13" t="s">
         <v>7</v>
@@ -1040,19 +1100,19 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.000000000000203200215153064</v>
+        <v>0.00000000000000000000000000000000000000000000202415104695448</v>
       </c>
       <c r="B14" t="n">
-        <v>1.36193170875766</v>
+        <v>1.28321952985707</v>
       </c>
       <c r="C14" t="n">
-        <v>0.457</v>
+        <v>0.826</v>
       </c>
       <c r="D14" t="n">
-        <v>0.279</v>
+        <v>0.482</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0000000074373310748173</v>
+        <v>0.0000000000000000000000000000000000000000740859524695811</v>
       </c>
       <c r="F14" t="s">
         <v>7</v>
@@ -1063,19 +1123,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.000000000000659107475873058</v>
+        <v>0.0000000000000000000000000000108138279449871</v>
       </c>
       <c r="B15" t="n">
-        <v>1.36042553491572</v>
+        <v>1.27343865730943</v>
       </c>
       <c r="C15" t="n">
-        <v>0.251</v>
+        <v>0.324</v>
       </c>
       <c r="D15" t="n">
-        <v>0.105</v>
+        <v>0.115</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0000000241239927244298</v>
+        <v>0.000000000000000000000000395796916614474</v>
       </c>
       <c r="F15" t="s">
         <v>7</v>
@@ -1086,19 +1146,19 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.000000000000000000000000316767104432702</v>
+        <v>0.00000000000000000000000000000198806926631891</v>
       </c>
       <c r="B16" t="n">
-        <v>1.31038479273147</v>
+        <v>1.26618762553429</v>
       </c>
       <c r="C16" t="n">
-        <v>0.429</v>
+        <v>0.295</v>
       </c>
       <c r="D16" t="n">
-        <v>0.176</v>
+        <v>0.094</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0000000000000000000115939927893413</v>
+        <v>0.0000000000000000000000000727653232165383</v>
       </c>
       <c r="F16" t="s">
         <v>7</v>
@@ -1109,19 +1169,19 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.000000000000000000000000000000615721332431978</v>
+        <v>0.0000000000000000000000000000000000000000242911939214213</v>
       </c>
       <c r="B17" t="n">
-        <v>1.30420400607774</v>
+        <v>1.26413592067734</v>
       </c>
       <c r="C17" t="n">
-        <v>0.578</v>
+        <v>0.414</v>
       </c>
       <c r="D17" t="n">
-        <v>0.279</v>
+        <v>0.142</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0000000000000000000000000225360164883428</v>
+        <v>0.000000000000000000000000000000000000889081988717942</v>
       </c>
       <c r="F17" t="s">
         <v>7</v>
@@ -1132,19 +1192,19 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.000000000215958421808409</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000508152654819956</v>
       </c>
       <c r="B18" t="n">
-        <v>1.29151254738149</v>
+        <v>1.21572570435975</v>
       </c>
       <c r="C18" t="n">
-        <v>0.32</v>
+        <v>0.968</v>
       </c>
       <c r="D18" t="n">
-        <v>0.176</v>
+        <v>0.475</v>
       </c>
       <c r="E18" t="n">
-        <v>0.00000790429419660957</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000185988953190652</v>
       </c>
       <c r="F18" t="s">
         <v>7</v>
@@ -1155,19 +1215,19 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.0000000000000000122628894156227</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000205460443279149</v>
       </c>
       <c r="B19" t="n">
-        <v>1.26610816638858</v>
+        <v>1.21543543346284</v>
       </c>
       <c r="C19" t="n">
-        <v>0.356</v>
+        <v>0.905</v>
       </c>
       <c r="D19" t="n">
-        <v>0.161</v>
+        <v>0.349</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000000000000448834015501206</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000752005768446013</v>
       </c>
       <c r="F19" t="s">
         <v>7</v>
@@ -1178,19 +1238,19 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.000000000000000000000000000000565215258665587</v>
+        <v>0.00000000000000000000000000000000000000000000350048197870142</v>
       </c>
       <c r="B20" t="n">
-        <v>1.24906927713538</v>
+        <v>1.19368491084536</v>
       </c>
       <c r="C20" t="n">
-        <v>0.895</v>
+        <v>0.529</v>
       </c>
       <c r="D20" t="n">
-        <v>0.76</v>
+        <v>0.212</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0000000000000000000000000206874436824192</v>
+        <v>0.000000000000000000000000000000000000000128121140902451</v>
       </c>
       <c r="F20" t="s">
         <v>7</v>
@@ -1201,19 +1261,19 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.000000000000144455536339929</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000328365014717975</v>
       </c>
       <c r="B21" t="n">
-        <v>1.23774434944238</v>
+        <v>1.17676306971238</v>
       </c>
       <c r="C21" t="n">
-        <v>0.29</v>
+        <v>0.753</v>
       </c>
       <c r="D21" t="n">
-        <v>0.13</v>
+        <v>0.318</v>
       </c>
       <c r="E21" t="n">
-        <v>0.00000000528721708557775</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000120184879036926</v>
       </c>
       <c r="F21" t="s">
         <v>7</v>
@@ -1224,19 +1284,19 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.000000000000000000000000000028795266881642</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000286605747027692</v>
       </c>
       <c r="B22" t="n">
-        <v>2.91535774745182</v>
+        <v>5.43465037888042</v>
       </c>
       <c r="C22" t="n">
-        <v>0.37</v>
+        <v>0.303</v>
       </c>
       <c r="D22" t="n">
-        <v>0.121</v>
+        <v>0.021</v>
       </c>
       <c r="E22" t="n">
-        <v>0.00000000000000000000000105393556313498</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000104900569469605</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -1247,19 +1307,19 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.00000000000000000000000000000000000000504454585280277</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000782401215106241</v>
       </c>
       <c r="B23" t="n">
-        <v>1.6185777484734</v>
+        <v>5.03298014145942</v>
       </c>
       <c r="C23" t="n">
-        <v>0.552</v>
+        <v>0.319</v>
       </c>
       <c r="D23" t="n">
-        <v>0.198</v>
+        <v>0.037</v>
       </c>
       <c r="E23" t="n">
-        <v>0.000000000000000000000000000000000184635422758434</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000286366668741035</v>
       </c>
       <c r="F23" t="s">
         <v>28</v>
@@ -1270,19 +1330,19 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.0000000000000000000000124523036621102</v>
+        <v>0.00000000000000000000000000000000000000711187034520822</v>
       </c>
       <c r="B24" t="n">
-        <v>1.58315542131228</v>
+        <v>3.37688269336537</v>
       </c>
       <c r="C24" t="n">
-        <v>0.508</v>
+        <v>0.308</v>
       </c>
       <c r="D24" t="n">
-        <v>0.243</v>
+        <v>0.099</v>
       </c>
       <c r="E24" t="n">
-        <v>0.000000000000000000455766766336896</v>
+        <v>0.000000000000000000000000000000000260301566504966</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -1293,19 +1353,19 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.00000000000000000000000000000000000000450420831962559</v>
+        <v>0.00000000000000000000000000464992619258684</v>
       </c>
       <c r="B25" t="n">
-        <v>1.51825177507973</v>
+        <v>3.02757955248615</v>
       </c>
       <c r="C25" t="n">
-        <v>0.742</v>
+        <v>0.338</v>
       </c>
       <c r="D25" t="n">
-        <v>0.373</v>
+        <v>0.164</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000000000000000000000000000000000164858528706616</v>
+        <v>0.000000000000000000000170191948574871</v>
       </c>
       <c r="F25" t="s">
         <v>28</v>
@@ -1316,19 +1376,19 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.00000000000000000000000000000000000000000000549674011199299</v>
+        <v>0.000000000000000220339440878531</v>
       </c>
       <c r="B26" t="n">
-        <v>1.51266109913656</v>
+        <v>2.96202045642131</v>
       </c>
       <c r="C26" t="n">
-        <v>0.568</v>
+        <v>0.291</v>
       </c>
       <c r="D26" t="n">
-        <v>0.18</v>
+        <v>0.169</v>
       </c>
       <c r="E26" t="n">
-        <v>0.000000000000000000000000000000000000000201186184839055</v>
+        <v>0.0000000000080646438755951</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -1339,19 +1399,19 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.00000000000000000000145868810553539</v>
+        <v>0.000000000000000000000000000000000000100263989155461</v>
       </c>
       <c r="B27" t="n">
-        <v>1.50278747755068</v>
+        <v>2.2729419903902</v>
       </c>
       <c r="C27" t="n">
-        <v>0.356</v>
+        <v>0.468</v>
       </c>
       <c r="D27" t="n">
-        <v>0.124</v>
+        <v>0.254</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0000000000000000533894433507008</v>
+        <v>0.00000000000000000000000000000000366976226707903</v>
       </c>
       <c r="F27" t="s">
         <v>28</v>
@@ -1362,19 +1422,19 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.000000000000000000000000000000000102302223966623</v>
+        <v>0.0000000000000197043855494741</v>
       </c>
       <c r="B28" t="n">
-        <v>1.47923409630925</v>
+        <v>2.21179346021801</v>
       </c>
       <c r="C28" t="n">
-        <v>0.707</v>
+        <v>0.258</v>
       </c>
       <c r="D28" t="n">
-        <v>0.352</v>
+        <v>0.142</v>
       </c>
       <c r="E28" t="n">
-        <v>0.00000000000000000000000000000374436369940235</v>
+        <v>0.000000000721200215496303</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -1385,19 +1445,19 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000221480302385366</v>
+        <v>0.00000000000000195788851430921</v>
       </c>
       <c r="B29" t="n">
-        <v>1.35077342182426</v>
+        <v>2.02904091277448</v>
       </c>
       <c r="C29" t="n">
-        <v>0.992</v>
+        <v>0.401</v>
       </c>
       <c r="D29" t="n">
-        <v>0.72</v>
+        <v>0.309</v>
       </c>
       <c r="E29" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000810640054760678</v>
+        <v>0.0000000000716606775122314</v>
       </c>
       <c r="F29" t="s">
         <v>28</v>
@@ -1408,19 +1468,19 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.000000000000136747821489676</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000243751446981619</v>
       </c>
       <c r="B30" t="n">
-        <v>1.33457208954498</v>
+        <v>2.0112081701032</v>
       </c>
       <c r="C30" t="n">
-        <v>0.274</v>
+        <v>0.467</v>
       </c>
       <c r="D30" t="n">
-        <v>0.112</v>
+        <v>0.02</v>
       </c>
       <c r="E30" t="n">
-        <v>0.00000000500510701434364</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000892154671097422</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -1431,19 +1491,19 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000117189376322598</v>
+        <v>0.000000000212209898142708</v>
       </c>
       <c r="B31" t="n">
-        <v>1.32815488612486</v>
+        <v>1.83432077410015</v>
       </c>
       <c r="C31" t="n">
-        <v>0.924</v>
+        <v>0.329</v>
       </c>
       <c r="D31" t="n">
-        <v>0.587</v>
+        <v>0.246</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0000000000000000000000000000000000000000000000042892483627834</v>
+        <v>0.00000776709448192127</v>
       </c>
       <c r="F31" t="s">
         <v>28</v>
@@ -1454,19 +1514,19 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.000000000000000000000000000000000000000952113971516059</v>
+        <v>0.000000000000000000000000000000000000000000000000000275346666340502</v>
       </c>
       <c r="B32" t="n">
-        <v>1.309592265957</v>
+        <v>1.80164958751754</v>
       </c>
       <c r="C32" t="n">
-        <v>0.658</v>
+        <v>0.773</v>
       </c>
       <c r="D32" t="n">
-        <v>0.273</v>
+        <v>0.81</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0000000000000000000000000000000000348483234714593</v>
+        <v>0.0000000000000000000000000000000000000000000000100779633347287</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -1477,19 +1537,19 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.0000000000000000000000000000000000000000000000705149208833556</v>
+        <v>0.00000000677912616456645</v>
       </c>
       <c r="B33" t="n">
-        <v>1.27479896006875</v>
+        <v>1.62842024150548</v>
       </c>
       <c r="C33" t="n">
-        <v>0.723</v>
+        <v>0.276</v>
       </c>
       <c r="D33" t="n">
-        <v>0.282</v>
+        <v>0.195</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0000000000000000000000000000000000000000025809166192517</v>
+        <v>0.000248122796749297</v>
       </c>
       <c r="F33" t="s">
         <v>28</v>
@@ -1500,19 +1560,19 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.00000000000000000000000020673543729439</v>
+        <v>0.0000000000020883955713905</v>
       </c>
       <c r="B34" t="n">
-        <v>1.25409699982243</v>
+        <v>1.58970382519873</v>
       </c>
       <c r="C34" t="n">
-        <v>0.747</v>
+        <v>0.319</v>
       </c>
       <c r="D34" t="n">
-        <v>0.469</v>
+        <v>0.212</v>
       </c>
       <c r="E34" t="n">
-        <v>0.00000000000000000000756672374041198</v>
+        <v>0.0000000764373663084638</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -1523,19 +1583,19 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.000000000000000995318569249449</v>
+        <v>0.0000000000000000000503163317002643</v>
       </c>
       <c r="B35" t="n">
-        <v>1.24908213064759</v>
+        <v>1.53644753019366</v>
       </c>
       <c r="C35" t="n">
-        <v>0.304</v>
+        <v>0.508</v>
       </c>
       <c r="D35" t="n">
-        <v>0.121</v>
+        <v>0.413</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0000000000364296549530991</v>
+        <v>0.00000000000000184162805656138</v>
       </c>
       <c r="F35" t="s">
         <v>28</v>
@@ -1546,19 +1606,19 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.000000000000000000000000000000000113891110111957</v>
+        <v>0.000000102984264121248</v>
       </c>
       <c r="B36" t="n">
-        <v>1.24513112008496</v>
+        <v>1.43040669696753</v>
       </c>
       <c r="C36" t="n">
-        <v>0.668</v>
+        <v>0.416</v>
       </c>
       <c r="D36" t="n">
-        <v>0.31</v>
+        <v>0.405</v>
       </c>
       <c r="E36" t="n">
-        <v>0.00000000000000000000000000000416852852120774</v>
+        <v>0.00376932705110181</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -1569,19 +1629,19 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.000000000000000000298324461964073</v>
+        <v>0.0007849425458187</v>
       </c>
       <c r="B37" t="n">
-        <v>1.22704857390147</v>
+        <v>1.40060000624826</v>
       </c>
       <c r="C37" t="n">
-        <v>0.318</v>
+        <v>0.326</v>
       </c>
       <c r="D37" t="n">
-        <v>0.11</v>
+        <v>0.323</v>
       </c>
       <c r="E37" t="n">
-        <v>0.000000000000010918973632347</v>
+        <v>1</v>
       </c>
       <c r="F37" t="s">
         <v>28</v>
@@ -1592,19 +1652,19 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.000000000000471039102596997</v>
+        <v>0.0000671049568477416</v>
       </c>
       <c r="B38" t="n">
-        <v>1.22564106711578</v>
+        <v>1.30342538289165</v>
       </c>
       <c r="C38" t="n">
-        <v>0.283</v>
+        <v>0.263</v>
       </c>
       <c r="D38" t="n">
-        <v>0.122</v>
+        <v>0.216</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0000000172405021941527</v>
+        <v>1</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -1615,19 +1675,19 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.0000000000000000000000000000000174222399684356</v>
+        <v>0.00000000252799683556338</v>
       </c>
       <c r="B39" t="n">
-        <v>1.20546794135453</v>
+        <v>1.29544990504537</v>
       </c>
       <c r="C39" t="n">
-        <v>0.639</v>
+        <v>0.512</v>
       </c>
       <c r="D39" t="n">
-        <v>0.297</v>
+        <v>0.552</v>
       </c>
       <c r="E39" t="n">
-        <v>0.000000000000000000000000000637671405084711</v>
+        <v>0.0000925272121784551</v>
       </c>
       <c r="F39" t="s">
         <v>28</v>
@@ -1638,19 +1698,19 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.00000000000000000000000000000000292657762893883</v>
+        <v>0.000000322988708428497</v>
       </c>
       <c r="B40" t="n">
-        <v>1.1890441515329</v>
+        <v>1.25002762895612</v>
       </c>
       <c r="C40" t="n">
-        <v>0.679</v>
+        <v>0.415</v>
       </c>
       <c r="D40" t="n">
-        <v>0.327</v>
+        <v>0.399</v>
       </c>
       <c r="E40" t="n">
-        <v>0.00000000000000000000000000010711566779679</v>
+        <v>0.0118217097171914</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -1661,19 +1721,19 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.000000000000000000000000532444318617227</v>
+        <v>0.00149617161033954</v>
       </c>
       <c r="B41" t="n">
-        <v>1.18841392118486</v>
+        <v>1.19074498348668</v>
       </c>
       <c r="C41" t="n">
-        <v>0.516</v>
+        <v>0.353</v>
       </c>
       <c r="D41" t="n">
-        <v>0.224</v>
+        <v>0.36</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0000000000000000000194879945057091</v>
+        <v>1</v>
       </c>
       <c r="F41" t="s">
         <v>28</v>
@@ -1684,19 +1744,19 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000873016360625574</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000283154653947191</v>
       </c>
       <c r="B42" t="n">
-        <v>4.999114657641</v>
+        <v>4.21573254820924</v>
       </c>
       <c r="C42" t="n">
-        <v>0.433</v>
+        <v>0.275</v>
       </c>
       <c r="D42" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000319532718152566</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000103637434891211</v>
       </c>
       <c r="F42" t="s">
         <v>49</v>
@@ -1707,19 +1767,19 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000470227244716782</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000997043874581316</v>
       </c>
       <c r="B43" t="n">
-        <v>4.69827269324516</v>
+        <v>3.54845320935035</v>
       </c>
       <c r="C43" t="n">
-        <v>0.269</v>
+        <v>0.813</v>
       </c>
       <c r="D43" t="n">
-        <v>0.007</v>
+        <v>0.176</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000172107873838789</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000364928028535507</v>
       </c>
       <c r="F43" t="s">
         <v>49</v>
@@ -1730,19 +1790,19 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000122400414325644</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000186025772829457</v>
       </c>
       <c r="B44" t="n">
-        <v>4.42684893710956</v>
+        <v>3.42433381472147</v>
       </c>
       <c r="C44" t="n">
-        <v>0.374</v>
+        <v>0.546</v>
       </c>
       <c r="D44" t="n">
-        <v>0.015</v>
+        <v>0.068</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000447997756473291</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000680872931133097</v>
       </c>
       <c r="F44" t="s">
         <v>49</v>
@@ -1753,19 +1813,19 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000383124147033046</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000672947128290982</v>
       </c>
       <c r="B45" t="n">
-        <v>4.33129391465491</v>
+        <v>3.41410783532021</v>
       </c>
       <c r="C45" t="n">
-        <v>0.928</v>
+        <v>0.729</v>
       </c>
       <c r="D45" t="n">
-        <v>0.097</v>
+        <v>0.076</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000140227269055565</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000246305378425782</v>
       </c>
       <c r="F45" t="s">
         <v>49</v>
@@ -1776,19 +1836,19 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000741135039293046</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000382800810047385</v>
       </c>
       <c r="B46" t="n">
-        <v>4.17250729408648</v>
+        <v>3.05961703542959</v>
       </c>
       <c r="C46" t="n">
-        <v>0.679</v>
+        <v>0.898</v>
       </c>
       <c r="D46" t="n">
-        <v>0.036</v>
+        <v>0.172</v>
       </c>
       <c r="E46" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000271262835731648</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000140108924485443</v>
       </c>
       <c r="F46" t="s">
         <v>49</v>
@@ -1799,19 +1859,19 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000257044461984876</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000448326018654501</v>
       </c>
       <c r="B47" t="n">
-        <v>4.15914789271331</v>
+        <v>2.97904869012283</v>
       </c>
       <c r="C47" t="n">
-        <v>0.354</v>
+        <v>0.338</v>
       </c>
       <c r="D47" t="n">
-        <v>0.016</v>
+        <v>0.039</v>
       </c>
       <c r="E47" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000940808435310843</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000164091806087734</v>
       </c>
       <c r="F47" t="s">
         <v>49</v>
@@ -1822,19 +1882,19 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000716022021491688</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000333640904701242</v>
       </c>
       <c r="B48" t="n">
-        <v>4.13040683389759</v>
+        <v>2.92170230381831</v>
       </c>
       <c r="C48" t="n">
-        <v>0.574</v>
+        <v>0.775</v>
       </c>
       <c r="D48" t="n">
-        <v>0.045</v>
+        <v>0.224</v>
       </c>
       <c r="E48" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000262071220086173</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000122115907529702</v>
       </c>
       <c r="F48" t="s">
         <v>49</v>
@@ -1845,19 +1905,19 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000230293386447853</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000771045250169135</v>
       </c>
       <c r="B49" t="n">
-        <v>4.03593679819955</v>
+        <v>2.90622997081354</v>
       </c>
       <c r="C49" t="n">
-        <v>0.734</v>
+        <v>0.609</v>
       </c>
       <c r="D49" t="n">
-        <v>0.057</v>
+        <v>0.072</v>
       </c>
       <c r="E49" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000842896823737788</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000282210272014405</v>
       </c>
       <c r="F49" t="s">
         <v>49</v>
@@ -1868,19 +1928,19 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000375665432614009</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000548659565611685</v>
       </c>
       <c r="B50" t="n">
-        <v>3.86107923864734</v>
+        <v>2.83637626040825</v>
       </c>
       <c r="C50" t="n">
-        <v>0.544</v>
+        <v>0.32</v>
       </c>
       <c r="D50" t="n">
-        <v>0.059</v>
+        <v>0.028</v>
       </c>
       <c r="E50" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000137497304991053</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000200814887609533</v>
       </c>
       <c r="F50" t="s">
         <v>49</v>
@@ -1891,19 +1951,19 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000166476966233704</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000102791256617912</v>
       </c>
       <c r="B51" t="n">
-        <v>3.79522726417771</v>
+        <v>2.74349634210147</v>
       </c>
       <c r="C51" t="n">
-        <v>0.833</v>
+        <v>0.599</v>
       </c>
       <c r="D51" t="n">
-        <v>0.131</v>
+        <v>0.172</v>
       </c>
       <c r="E51" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000060932234411198</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000376226278347221</v>
       </c>
       <c r="F51" t="s">
         <v>49</v>
@@ -1914,19 +1974,19 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000957737006661806</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000019858191042402</v>
       </c>
       <c r="B52" t="n">
-        <v>3.60651306934861</v>
+        <v>2.70389918944438</v>
       </c>
       <c r="C52" t="n">
-        <v>0.793</v>
+        <v>0.486</v>
       </c>
       <c r="D52" t="n">
-        <v>0.157</v>
+        <v>0.09</v>
       </c>
       <c r="E52" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000350541321808288</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000726829650342956</v>
       </c>
       <c r="F52" t="s">
         <v>49</v>
@@ -1937,19 +1997,19 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000639456870480644</v>
+        <v>0.00000000000000000000000000000134587644804054</v>
       </c>
       <c r="B53" t="n">
-        <v>3.56215214744565</v>
+        <v>2.68792884915768</v>
       </c>
       <c r="C53" t="n">
-        <v>0.387</v>
+        <v>0.313</v>
       </c>
       <c r="D53" t="n">
-        <v>0.02</v>
+        <v>0.086</v>
       </c>
       <c r="E53" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000023404760916462</v>
+        <v>0.0000000000000000000000000492604238747319</v>
       </c>
       <c r="F53" t="s">
         <v>49</v>
@@ -1960,19 +2020,19 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000019435020628542</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000003507387820637</v>
       </c>
       <c r="B54" t="n">
-        <v>3.54112053849934</v>
+        <v>2.64228677034553</v>
       </c>
       <c r="C54" t="n">
-        <v>0.649</v>
+        <v>0.356</v>
       </c>
       <c r="D54" t="n">
-        <v>0.108</v>
+        <v>0.036</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000711341190025265</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000128373901623135</v>
       </c>
       <c r="F54" t="s">
         <v>49</v>
@@ -1983,19 +2043,19 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000638978689809604</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000385595123322586</v>
       </c>
       <c r="B55" t="n">
-        <v>3.34193998496257</v>
+        <v>2.58951846539387</v>
       </c>
       <c r="C55" t="n">
-        <v>0.357</v>
+        <v>0.521</v>
       </c>
       <c r="D55" t="n">
-        <v>0.023</v>
+        <v>0.077</v>
       </c>
       <c r="E55" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000233872590257213</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000001411316710873</v>
       </c>
       <c r="F55" t="s">
         <v>49</v>
@@ -2006,19 +2066,19 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000477948942492539</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000156940688454585</v>
       </c>
       <c r="B56" t="n">
-        <v>3.31418738194324</v>
+        <v>2.5851508802779</v>
       </c>
       <c r="C56" t="n">
-        <v>0.557</v>
+        <v>0.472</v>
       </c>
       <c r="D56" t="n">
-        <v>0.076</v>
+        <v>0.083</v>
       </c>
       <c r="E56" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000174934092441694</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000574418613812627</v>
       </c>
       <c r="F56" t="s">
         <v>49</v>
@@ -2029,19 +2089,19 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.000000000000000000000000000000000000000000789207178986869</v>
+        <v>0.000000000000000000000000000000000753126219882298</v>
       </c>
       <c r="B57" t="n">
-        <v>3.22261276887701</v>
+        <v>2.55133567068622</v>
       </c>
       <c r="C57" t="n">
-        <v>0.256</v>
+        <v>0.275</v>
       </c>
       <c r="D57" t="n">
-        <v>0.024</v>
+        <v>0.059</v>
       </c>
       <c r="E57" t="n">
-        <v>0.0000000000000000000000000000000000000288857719580984</v>
+        <v>0.000000000000000000000000000027565172773912</v>
       </c>
       <c r="F57" t="s">
         <v>49</v>
@@ -2052,19 +2112,19 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000895842667838931</v>
+        <v>0.0000000000000000000000000000000000000000000000000412990555483523</v>
       </c>
       <c r="B58" t="n">
-        <v>3.12597205407635</v>
+        <v>2.52806613623477</v>
       </c>
       <c r="C58" t="n">
-        <v>0.59</v>
+        <v>0.32</v>
       </c>
       <c r="D58" t="n">
-        <v>0.064</v>
+        <v>0.051</v>
       </c>
       <c r="E58" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000327887374855727</v>
+        <v>0.00000000000000000000000000000000000000000000151158673212524</v>
       </c>
       <c r="F58" t="s">
         <v>49</v>
@@ -2075,19 +2135,19 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000234053280093141</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000554805884105355</v>
       </c>
       <c r="B59" t="n">
-        <v>3.10675498139781</v>
+        <v>2.49763025549161</v>
       </c>
       <c r="C59" t="n">
-        <v>0.446</v>
+        <v>0.63</v>
       </c>
       <c r="D59" t="n">
-        <v>0.04</v>
+        <v>0.144</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000856658410468904</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000203064501641401</v>
       </c>
       <c r="F59" t="s">
         <v>49</v>
@@ -2098,19 +2158,19 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.00000000000000000000000000000000000000000263872008748868</v>
+        <v>0.000000000000000000000000000000000260394238811513</v>
       </c>
       <c r="B60" t="n">
-        <v>3.09480641818992</v>
+        <v>2.469246578774</v>
       </c>
       <c r="C60" t="n">
-        <v>0.279</v>
+        <v>0.25</v>
       </c>
       <c r="D60" t="n">
-        <v>0.033</v>
+        <v>0.046</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0000000000000000000000000000000000000965797939221732</v>
+        <v>0.00000000000000000000000000000953068953474019</v>
       </c>
       <c r="F60" t="s">
         <v>49</v>
@@ -2121,19 +2181,19 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000142624054777617</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000062594638183435</v>
       </c>
       <c r="B61" t="n">
-        <v>3.08170593009635</v>
+        <v>2.46845465175662</v>
       </c>
       <c r="C61" t="n">
-        <v>0.984</v>
+        <v>0.32</v>
       </c>
       <c r="D61" t="n">
-        <v>0.269</v>
+        <v>0.041</v>
       </c>
       <c r="E61" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000522018302891557</v>
+        <v>0.000000000000000000000000000000000000000000000000000022910263521519</v>
       </c>
       <c r="F61" t="s">
         <v>49</v>
@@ -2144,19 +2204,19 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000593011431241822</v>
+        <v>0.0000000000000000000000000000000000000000000000017171564331828</v>
       </c>
       <c r="B62" t="n">
-        <v>5.41801936632455</v>
+        <v>2.7584263516805</v>
       </c>
       <c r="C62" t="n">
-        <v>0.292</v>
+        <v>0.379</v>
       </c>
       <c r="D62" t="n">
-        <v>0.02</v>
+        <v>0.074</v>
       </c>
       <c r="E62" t="n">
-        <v>0.000000000000000000000000000000000000000000000000217048113948819</v>
+        <v>0.0000000000000000000000000000000000000000000628496426109235</v>
       </c>
       <c r="F62" t="s">
         <v>70</v>
@@ -2167,19 +2227,19 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.0000000000000000000000000000000000000493327472239474</v>
+        <v>0.00000000000000000000000000000000000000351100828012291</v>
       </c>
       <c r="B63" t="n">
-        <v>4.65805727254665</v>
+        <v>2.04940008072516</v>
       </c>
       <c r="C63" t="n">
-        <v>0.292</v>
+        <v>0.454</v>
       </c>
       <c r="D63" t="n">
-        <v>0.042</v>
+        <v>0.13</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0000000000000000000000000000000018056278811437</v>
+        <v>0.000000000000000000000000000000000128506414060779</v>
       </c>
       <c r="F63" t="s">
         <v>70</v>
@@ -2190,19 +2250,19 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.0000000000000000000000000246018597660805</v>
+        <v>0.000000000000000000000000210464711280875</v>
       </c>
       <c r="B64" t="n">
-        <v>3.41991346582704</v>
+        <v>1.99169872365191</v>
       </c>
       <c r="C64" t="n">
-        <v>0.343</v>
+        <v>0.283</v>
       </c>
       <c r="D64" t="n">
-        <v>0.098</v>
+        <v>0.073</v>
       </c>
       <c r="E64" t="n">
-        <v>0.000000000000000000000900452669298313</v>
+        <v>0.00000000000000000000770321889759132</v>
       </c>
       <c r="F64" t="s">
         <v>70</v>
@@ -2213,19 +2273,19 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.0000000000000000000111805456600722</v>
+        <v>0.000000000000000000000000184574800881898</v>
       </c>
       <c r="B65" t="n">
-        <v>3.09580656014963</v>
+        <v>1.584697268389</v>
       </c>
       <c r="C65" t="n">
-        <v>0.38</v>
+        <v>0.496</v>
       </c>
       <c r="D65" t="n">
-        <v>0.155</v>
+        <v>0.203</v>
       </c>
       <c r="E65" t="n">
-        <v>0.000000000000000409219151704304</v>
+        <v>0.00000000000000000000675562228707837</v>
       </c>
       <c r="F65" t="s">
         <v>70</v>
@@ -2236,19 +2296,19 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.0000000185196070248245</v>
+        <v>0.000000000000000000000000000000000000000000000586804404354503</v>
       </c>
       <c r="B66" t="n">
-        <v>2.66219074160194</v>
+        <v>1.5814990212867</v>
       </c>
       <c r="C66" t="n">
-        <v>0.306</v>
+        <v>0.721</v>
       </c>
       <c r="D66" t="n">
-        <v>0.183</v>
+        <v>0.303</v>
       </c>
       <c r="E66" t="n">
-        <v>0.000677836136715601</v>
+        <v>0.0000000000000000000000000000000000000000214776280037792</v>
       </c>
       <c r="F66" t="s">
         <v>70</v>
@@ -2259,19 +2319,19 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.00000000000000577555803826699</v>
+        <v>0.000000000000000000000000000000000102058021504846</v>
       </c>
       <c r="B67" t="n">
-        <v>2.41803097258725</v>
+        <v>1.52836276697433</v>
       </c>
       <c r="C67" t="n">
-        <v>0.366</v>
+        <v>0.546</v>
       </c>
       <c r="D67" t="n">
-        <v>0.176</v>
+        <v>0.194</v>
       </c>
       <c r="E67" t="n">
-        <v>0.00000000021139119975861</v>
+        <v>0.00000000000000000000000000000373542564509886</v>
       </c>
       <c r="F67" t="s">
         <v>70</v>
@@ -2282,19 +2342,19 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.000000000000000000000119016783576269</v>
+        <v>0.000000000000000692477464993581</v>
       </c>
       <c r="B68" t="n">
-        <v>2.38032638330629</v>
+        <v>1.42908904748124</v>
       </c>
       <c r="C68" t="n">
-        <v>0.514</v>
+        <v>0.317</v>
       </c>
       <c r="D68" t="n">
-        <v>0.267</v>
+        <v>0.124</v>
       </c>
       <c r="E68" t="n">
-        <v>0.00000000000000000435613329567504</v>
+        <v>0.0000000000253453676962301</v>
       </c>
       <c r="F68" t="s">
         <v>70</v>
@@ -2305,19 +2365,19 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.000000054233073694543</v>
+        <v>0.00000000000137924412048196</v>
       </c>
       <c r="B69" t="n">
-        <v>2.37448995478512</v>
+        <v>1.41433476155802</v>
       </c>
       <c r="C69" t="n">
-        <v>0.255</v>
+        <v>0.254</v>
       </c>
       <c r="D69" t="n">
-        <v>0.134</v>
+        <v>0.101</v>
       </c>
       <c r="E69" t="n">
-        <v>0.00198498473029397</v>
+        <v>0.0000000504817140537603</v>
       </c>
       <c r="F69" t="s">
         <v>70</v>
@@ -2328,19 +2388,19 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.00000000701831723538784</v>
+        <v>0.000000000000000000000000000000000170244962005248</v>
       </c>
       <c r="B70" t="n">
-        <v>2.31507853256187</v>
+        <v>1.37450419601575</v>
       </c>
       <c r="C70" t="n">
-        <v>0.273</v>
+        <v>0.65</v>
       </c>
       <c r="D70" t="n">
-        <v>0.143</v>
+        <v>0.291</v>
       </c>
       <c r="E70" t="n">
-        <v>0.00025687742913243</v>
+        <v>0.00000000000000000000000000000623113585435409</v>
       </c>
       <c r="F70" t="s">
         <v>70</v>
@@ -2351,19 +2411,19 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000148165279008671</v>
+        <v>0.00000000000000000000000000000000000499543447677452</v>
       </c>
       <c r="B71" t="n">
-        <v>2.26803182255064</v>
+        <v>1.30115903782538</v>
       </c>
       <c r="C71" t="n">
-        <v>0.389</v>
+        <v>0.625</v>
       </c>
       <c r="D71" t="n">
-        <v>0.015</v>
+        <v>0.252</v>
       </c>
       <c r="E71" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000542299737699637</v>
+        <v>0.000000000000000000000000000000182837897284424</v>
       </c>
       <c r="F71" t="s">
         <v>70</v>
@@ -2374,19 +2434,19 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.00000000124218791692632</v>
+        <v>0.000000000000000000000302125767351931</v>
       </c>
       <c r="B72" t="n">
-        <v>2.20915869551294</v>
+        <v>1.29845839935376</v>
       </c>
       <c r="C72" t="n">
-        <v>0.269</v>
+        <v>0.404</v>
       </c>
       <c r="D72" t="n">
-        <v>0.13</v>
+        <v>0.155</v>
       </c>
       <c r="E72" t="n">
-        <v>0.0000454653199474203</v>
+        <v>0.000000000000000011058105210848</v>
       </c>
       <c r="F72" t="s">
         <v>70</v>
@@ -2397,19 +2457,19 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.000000779941213339209</v>
+        <v>0.000000000000000000000000000000000000000000023507296363026</v>
       </c>
       <c r="B73" t="n">
-        <v>1.94363501348332</v>
+        <v>1.25258307152582</v>
       </c>
       <c r="C73" t="n">
-        <v>0.255</v>
+        <v>0.933</v>
       </c>
       <c r="D73" t="n">
-        <v>0.14</v>
+        <v>0.574</v>
       </c>
       <c r="E73" t="n">
-        <v>0.0285466283494284</v>
+        <v>0.000000000000000000000000000000000000000860390554183116</v>
       </c>
       <c r="F73" t="s">
         <v>70</v>
@@ -2420,19 +2480,19 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.000000000000000000000000000000000000116470841478294</v>
+        <v>0.000000000000000000000000000807426416637556</v>
       </c>
       <c r="B74" t="n">
-        <v>1.86845076324978</v>
+        <v>1.23534274637974</v>
       </c>
       <c r="C74" t="n">
-        <v>0.454</v>
+        <v>0.642</v>
       </c>
       <c r="D74" t="n">
-        <v>0.107</v>
+        <v>0.301</v>
       </c>
       <c r="E74" t="n">
-        <v>0.00000000000000000000000000000000426294926894706</v>
+        <v>0.0000000000000000000000295526142753512</v>
       </c>
       <c r="F74" t="s">
         <v>70</v>
@@ -2443,19 +2503,19 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.000000571366603898884</v>
+        <v>0.00000000000121190576765432</v>
       </c>
       <c r="B75" t="n">
-        <v>1.79523063828876</v>
+        <v>1.22243768249152</v>
       </c>
       <c r="C75" t="n">
-        <v>0.31</v>
+        <v>0.258</v>
       </c>
       <c r="D75" t="n">
-        <v>0.198</v>
+        <v>0.101</v>
       </c>
       <c r="E75" t="n">
-        <v>0.020912589069303</v>
+        <v>0.0000000443569630019159</v>
       </c>
       <c r="F75" t="s">
         <v>70</v>
@@ -2466,19 +2526,19 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.0000160318731498439</v>
+        <v>0.000000000000076742710144895</v>
       </c>
       <c r="B76" t="n">
-        <v>1.71158457868212</v>
+        <v>1.2203116845715</v>
       </c>
       <c r="C76" t="n">
-        <v>0.347</v>
+        <v>0.317</v>
       </c>
       <c r="D76" t="n">
-        <v>0.254</v>
+        <v>0.132</v>
       </c>
       <c r="E76" t="n">
-        <v>0.586782589157437</v>
+        <v>0.0000000028088599340133</v>
       </c>
       <c r="F76" t="s">
         <v>70</v>
@@ -2489,19 +2549,19 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.000000843569433803204</v>
+        <v>0.0000000000000000000206748229826256</v>
       </c>
       <c r="B77" t="n">
-        <v>1.70946220858827</v>
+        <v>1.19712840351801</v>
       </c>
       <c r="C77" t="n">
-        <v>0.398</v>
+        <v>0.521</v>
       </c>
       <c r="D77" t="n">
-        <v>0.315</v>
+        <v>0.256</v>
       </c>
       <c r="E77" t="n">
-        <v>0.0308754848466311</v>
+        <v>0.00000000000000075671919598708</v>
       </c>
       <c r="F77" t="s">
         <v>70</v>
@@ -2512,19 +2572,19 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.0000847279806051135</v>
+        <v>0.0000000000000148058396379884</v>
       </c>
       <c r="B78" t="n">
-        <v>1.66152269880311</v>
+        <v>1.19554351719246</v>
       </c>
       <c r="C78" t="n">
-        <v>0.38</v>
+        <v>0.342</v>
       </c>
       <c r="D78" t="n">
-        <v>0.325</v>
+        <v>0.147</v>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>0.000000000541908536590013</v>
       </c>
       <c r="F78" t="s">
         <v>70</v>
@@ -2535,19 +2595,19 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0.000448015628450484</v>
+        <v>0.000000000000000000000000337781274809127</v>
       </c>
       <c r="B79" t="n">
-        <v>1.6463230478507</v>
+        <v>1.18457839779934</v>
       </c>
       <c r="C79" t="n">
-        <v>0.324</v>
+        <v>0.675</v>
       </c>
       <c r="D79" t="n">
-        <v>0.26</v>
+        <v>0.364</v>
       </c>
       <c r="E79" t="n">
-        <v>1</v>
+        <v>0.0000000000000000000123631324392889</v>
       </c>
       <c r="F79" t="s">
         <v>70</v>
@@ -2558,19 +2618,19 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.000621071255673862</v>
+        <v>0.000000000000000969463333517106</v>
       </c>
       <c r="B80" t="n">
-        <v>1.60648686597608</v>
+        <v>1.17739044671617</v>
       </c>
       <c r="C80" t="n">
-        <v>0.278</v>
+        <v>0.35</v>
       </c>
       <c r="D80" t="n">
-        <v>0.209</v>
+        <v>0.147</v>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>0.0000000000354833274700596</v>
       </c>
       <c r="F80" t="s">
         <v>70</v>
@@ -2581,19 +2641,19 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.000000000115476384243642</v>
+        <v>0.0000000000000000718923990806772</v>
       </c>
       <c r="B81" t="n">
-        <v>1.58938966303968</v>
+        <v>1.17716520550879</v>
       </c>
       <c r="C81" t="n">
-        <v>0.519</v>
+        <v>0.471</v>
       </c>
       <c r="D81" t="n">
-        <v>0.411</v>
+        <v>0.228</v>
       </c>
       <c r="E81" t="n">
-        <v>0.00000422655113970155</v>
+        <v>0.00000000000263133369875187</v>
       </c>
       <c r="F81" t="s">
         <v>70</v>
@@ -2604,19 +2664,19 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000146247560494329</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000087592124875952</v>
       </c>
       <c r="B82" t="n">
-        <v>7.15726968776152</v>
+        <v>5.39908215749355</v>
       </c>
       <c r="C82" t="n">
-        <v>0.932</v>
+        <v>0.816</v>
       </c>
       <c r="D82" t="n">
-        <v>0.015</v>
+        <v>0.039</v>
       </c>
       <c r="E82" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000535280696165294</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000320595936258472</v>
       </c>
       <c r="F82" t="s">
         <v>91</v>
@@ -2627,19 +2687,19 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000014708954575662</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000348608213093519</v>
       </c>
       <c r="B83" t="n">
-        <v>6.54506422106635</v>
+        <v>5.18714928817782</v>
       </c>
       <c r="C83" t="n">
-        <v>0.523</v>
+        <v>0.322</v>
       </c>
       <c r="D83" t="n">
-        <v>0.018</v>
+        <v>0.01</v>
       </c>
       <c r="E83" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000538362446423806</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000127594092074359</v>
       </c>
       <c r="F83" t="s">
         <v>91</v>
@@ -2650,19 +2710,19 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000199401424247113</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000023306673811095</v>
       </c>
       <c r="B84" t="n">
-        <v>6.39455355819298</v>
+        <v>5.1128642800058</v>
       </c>
       <c r="C84" t="n">
-        <v>0.977</v>
+        <v>0.345</v>
       </c>
       <c r="D84" t="n">
-        <v>0.093</v>
+        <v>0.013</v>
       </c>
       <c r="E84" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000729829152886857</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000853047568159889</v>
       </c>
       <c r="F84" t="s">
         <v>91</v>
@@ -2673,19 +2733,19 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000186207222376312</v>
+        <v>0.00000000000000000000000000000000000000666122964271951</v>
       </c>
       <c r="B85" t="n">
-        <v>6.23109745468853</v>
+        <v>4.67599868545</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>0.276</v>
       </c>
       <c r="D85" t="n">
-        <v>0.033</v>
+        <v>0.023</v>
       </c>
       <c r="E85" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000068153705461954</v>
+        <v>0.000000000000000000000000000000000243807666153177</v>
       </c>
       <c r="F85" t="s">
         <v>91</v>
@@ -2696,19 +2756,19 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000183235739397719</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000479784027339138</v>
       </c>
       <c r="B86" t="n">
-        <v>6.12411311980792</v>
+        <v>4.62147137054517</v>
       </c>
       <c r="C86" t="n">
-        <v>0.864</v>
+        <v>0.529</v>
       </c>
       <c r="D86" t="n">
-        <v>0.015</v>
+        <v>0.026</v>
       </c>
       <c r="E86" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000670661129769592</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000175605751846398</v>
       </c>
       <c r="F86" t="s">
         <v>91</v>
@@ -2719,19 +2779,19 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000308725889960189</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000708566453678396</v>
       </c>
       <c r="B87" t="n">
-        <v>5.38021255282333</v>
+        <v>4.24003742958424</v>
       </c>
       <c r="C87" t="n">
-        <v>0.955</v>
+        <v>0.609</v>
       </c>
       <c r="D87" t="n">
-        <v>0.054</v>
+        <v>0.051</v>
       </c>
       <c r="E87" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000112996762984329</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000025934240771083</v>
       </c>
       <c r="F87" t="s">
         <v>91</v>
@@ -2742,19 +2802,19 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0.000000000000000000000000000000000177953989907809</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000711948340947108</v>
       </c>
       <c r="B88" t="n">
-        <v>3.92163078150557</v>
+        <v>4.23540673216335</v>
       </c>
       <c r="C88" t="n">
-        <v>0.955</v>
+        <v>0.931</v>
       </c>
       <c r="D88" t="n">
-        <v>0.267</v>
+        <v>0.111</v>
       </c>
       <c r="E88" t="n">
-        <v>0.00000000000000000000000000000651329398461572</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000260580212270051</v>
       </c>
       <c r="F88" t="s">
         <v>91</v>
@@ -2765,19 +2825,19 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0.0000000000000000000000000000000223906366122156</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000178593907377553</v>
       </c>
       <c r="B89" t="n">
-        <v>3.69839048184854</v>
+        <v>4.13186408746655</v>
       </c>
       <c r="C89" t="n">
-        <v>0.386</v>
+        <v>0.943</v>
       </c>
       <c r="D89" t="n">
-        <v>0.029</v>
+        <v>0.235</v>
       </c>
       <c r="E89" t="n">
-        <v>0.000000000000000000000000000819519690643702</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000653671560392581</v>
       </c>
       <c r="F89" t="s">
         <v>91</v>
@@ -2788,19 +2848,19 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0.00000000000000000000000000239788092351955</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000506074960990193</v>
       </c>
       <c r="B90" t="n">
-        <v>3.4133396249452</v>
+        <v>4.12482864007591</v>
       </c>
       <c r="C90" t="n">
-        <v>0.341</v>
+        <v>0.805</v>
       </c>
       <c r="D90" t="n">
-        <v>0.026</v>
+        <v>0.068</v>
       </c>
       <c r="E90" t="n">
-        <v>0.0000000000000000000000877648396817391</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000185228496472021</v>
       </c>
       <c r="F90" t="s">
         <v>91</v>
@@ -2811,19 +2871,19 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>0.00000000000000000000903391591091543</v>
+        <v>0.0000000000000000000000000000000000000000000000000290259948306883</v>
       </c>
       <c r="B91" t="n">
-        <v>3.21738058047068</v>
+        <v>3.42165178480216</v>
       </c>
       <c r="C91" t="n">
-        <v>0.273</v>
+        <v>0.448</v>
       </c>
       <c r="D91" t="n">
-        <v>0.023</v>
+        <v>0.049</v>
       </c>
       <c r="E91" t="n">
-        <v>0.000000000000000330650356255416</v>
+        <v>0.00000000000000000000000000000000000000000000106238043679802</v>
       </c>
       <c r="F91" t="s">
         <v>91</v>
@@ -2834,19 +2894,19 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.00000000000197909145689929</v>
+        <v>0.0000000000000000000000000000000000000000000000000000271828469177637</v>
       </c>
       <c r="B92" t="n">
-        <v>2.32326220441529</v>
+        <v>3.41298441301018</v>
       </c>
       <c r="C92" t="n">
-        <v>0.545</v>
+        <v>0.839</v>
       </c>
       <c r="D92" t="n">
-        <v>0.165</v>
+        <v>0.233</v>
       </c>
       <c r="E92" t="n">
-        <v>0.0000000724367264139708</v>
+        <v>0.00000000000000000000000000000000000000000000000099491938003707</v>
       </c>
       <c r="F92" t="s">
         <v>91</v>
@@ -2857,19 +2917,19 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>0.000000000000000000000000165332757209272</v>
+        <v>0.0000000000000000000000000000000000000567576349242243</v>
       </c>
       <c r="B93" t="n">
-        <v>2.24029049537789</v>
+        <v>3.38684612309429</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>0.276</v>
       </c>
       <c r="D93" t="n">
-        <v>0.456</v>
+        <v>0.023</v>
       </c>
       <c r="E93" t="n">
-        <v>0.00000000000000000000605134424661655</v>
+        <v>0.00000000000000000000000000000000207738619586153</v>
       </c>
       <c r="F93" t="s">
         <v>91</v>
@@ -2880,19 +2940,19 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0.0000000318672699312862</v>
+        <v>0.00000000000000000000000418722914982793</v>
       </c>
       <c r="B94" t="n">
-        <v>2.21447132253124</v>
+        <v>3.37072363153731</v>
       </c>
       <c r="C94" t="n">
-        <v>0.25</v>
+        <v>0.264</v>
       </c>
       <c r="D94" t="n">
-        <v>0.051</v>
+        <v>0.036</v>
       </c>
       <c r="E94" t="n">
-        <v>0.00116637394675501</v>
+        <v>0.000000000000000000153256774112852</v>
       </c>
       <c r="F94" t="s">
         <v>91</v>
@@ -2903,19 +2963,19 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0.00000000000142422225125037</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000421239225665439</v>
       </c>
       <c r="B95" t="n">
-        <v>2.15619472957127</v>
+        <v>3.26274296286041</v>
       </c>
       <c r="C95" t="n">
-        <v>0.409</v>
+        <v>0.586</v>
       </c>
       <c r="D95" t="n">
-        <v>0.081</v>
+        <v>0.065</v>
       </c>
       <c r="E95" t="n">
-        <v>0.0000000521279586180148</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000154177768985807</v>
       </c>
       <c r="F95" t="s">
         <v>91</v>
@@ -2926,19 +2986,19 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0.00000000000075228263259688</v>
+        <v>0.0000000000000000000000000000000000000000000000000130696848959848</v>
       </c>
       <c r="B96" t="n">
-        <v>2.12525937178679</v>
+        <v>3.2377836693669</v>
       </c>
       <c r="C96" t="n">
-        <v>0.432</v>
+        <v>0.517</v>
       </c>
       <c r="D96" t="n">
-        <v>0.09</v>
+        <v>0.067</v>
       </c>
       <c r="E96" t="n">
-        <v>0.0000000275342966356784</v>
+        <v>0.000000000000000000000000000000000000000000000478363536877941</v>
       </c>
       <c r="F96" t="s">
         <v>91</v>
@@ -2949,19 +3009,19 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>0.0000000252021771488112</v>
+        <v>0.0000000000000000000000000000351611086587659</v>
       </c>
       <c r="B97" t="n">
-        <v>1.94695891148844</v>
+        <v>3.09109312781939</v>
       </c>
       <c r="C97" t="n">
-        <v>0.273</v>
+        <v>0.299</v>
       </c>
       <c r="D97" t="n">
-        <v>0.059</v>
+        <v>0.037</v>
       </c>
       <c r="E97" t="n">
-        <v>0.000922424885823637</v>
+        <v>0.00000000000000000000000128693173801949</v>
       </c>
       <c r="F97" t="s">
         <v>91</v>
@@ -2972,19 +3032,19 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0.00000000000408242738944972</v>
+        <v>0.000000000000000000000000000187016112493088</v>
       </c>
       <c r="B98" t="n">
-        <v>1.78458113615724</v>
+        <v>3.01080619436649</v>
       </c>
       <c r="C98" t="n">
-        <v>0.545</v>
+        <v>0.276</v>
       </c>
       <c r="D98" t="n">
-        <v>0.153</v>
+        <v>0.032</v>
       </c>
       <c r="E98" t="n">
-        <v>0.000000149420924881249</v>
+        <v>0.00000000000000000000000684497673335952</v>
       </c>
       <c r="F98" t="s">
         <v>91</v>
@@ -2995,19 +3055,19 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>0.00000000260567272655875</v>
+        <v>0.000000000000000000000000000000023889344806767</v>
       </c>
       <c r="B99" t="n">
-        <v>1.74605274882144</v>
+        <v>2.95764751095854</v>
       </c>
       <c r="C99" t="n">
-        <v>0.523</v>
+        <v>0.379</v>
       </c>
       <c r="D99" t="n">
-        <v>0.169</v>
+        <v>0.054</v>
       </c>
       <c r="E99" t="n">
-        <v>0.0000953702274647768</v>
+        <v>0.000000000000000000000000000874373909272479</v>
       </c>
       <c r="F99" t="s">
         <v>91</v>
@@ -3018,19 +3078,19 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>0.00000359920853832303</v>
+        <v>0.000000000000000000000000000833915653214687</v>
       </c>
       <c r="B100" t="n">
-        <v>1.67292182856341</v>
+        <v>2.80645430264308</v>
       </c>
       <c r="C100" t="n">
-        <v>0.25</v>
+        <v>0.414</v>
       </c>
       <c r="D100" t="n">
-        <v>0.064</v>
+        <v>0.078</v>
       </c>
       <c r="E100" t="n">
-        <v>0.131734631711161</v>
+        <v>0.0000000000000000000000305221468233108</v>
       </c>
       <c r="F100" t="s">
         <v>91</v>
@@ -3041,485 +3101,945 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>0.000108230472141048</v>
+        <v>0.0000000000000000000000000000000000000000000000061069071995694</v>
       </c>
       <c r="B101" t="n">
-        <v>1.66096302239144</v>
+        <v>2.7160960354131</v>
       </c>
       <c r="C101" t="n">
-        <v>0.25</v>
+        <v>0.782</v>
       </c>
       <c r="D101" t="n">
-        <v>0.082</v>
+        <v>0.185</v>
       </c>
       <c r="E101" t="n">
-        <v>1</v>
+        <v>0.00000000000000000000000000000000000000000022351891041144</v>
       </c>
       <c r="F101" t="s">
         <v>91</v>
       </c>
       <c r="G101" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>0.0000000000891377465958589</v>
+        <v>1.60898011339045e-247</v>
       </c>
       <c r="B102" t="n">
-        <v>4.65588807281658</v>
+        <v>6.92963081033423</v>
       </c>
       <c r="C102" t="n">
-        <v>0.294</v>
+        <v>0.914</v>
       </c>
       <c r="D102" t="n">
-        <v>0.05</v>
+        <v>0.018</v>
       </c>
       <c r="E102" t="n">
-        <v>0.00000326253066315503</v>
+        <v>5.88902811302037e-243</v>
       </c>
       <c r="F102" t="s">
+        <v>111</v>
+      </c>
+      <c r="G102" t="s">
         <v>112</v>
-      </c>
-      <c r="G102" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>0.00000000000000000000000500746984970178</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000012946407753194</v>
       </c>
       <c r="B103" t="n">
-        <v>3.94225486699184</v>
+        <v>6.52580248827216</v>
       </c>
       <c r="C103" t="n">
-        <v>0.735</v>
+        <v>0.517</v>
       </c>
       <c r="D103" t="n">
-        <v>0.162</v>
+        <v>0.016</v>
       </c>
       <c r="E103" t="n">
-        <v>0.000000000000000000183278403968935</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000473851470174655</v>
       </c>
       <c r="F103" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G103" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>0.0000000000000747246764651701</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000780288664059465</v>
       </c>
       <c r="B104" t="n">
-        <v>3.90297617890739</v>
+        <v>6.42142705315617</v>
       </c>
       <c r="C104" t="n">
-        <v>0.382</v>
+        <v>0.983</v>
       </c>
       <c r="D104" t="n">
-        <v>0.065</v>
+        <v>0.097</v>
       </c>
       <c r="E104" t="n">
-        <v>0.00000000273499788330169</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000285593453932405</v>
       </c>
       <c r="F104" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G104" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>0.000000000611908560768432</v>
+        <v>4.14558817042337e-222</v>
       </c>
       <c r="B105" t="n">
-        <v>3.82677259403004</v>
+        <v>5.94589684288956</v>
       </c>
       <c r="C105" t="n">
-        <v>0.382</v>
+        <v>0.828</v>
       </c>
       <c r="D105" t="n">
-        <v>0.088</v>
+        <v>0.015</v>
       </c>
       <c r="E105" t="n">
-        <v>0.0000223964652326854</v>
+        <v>1.51732672625666e-217</v>
       </c>
       <c r="F105" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G105" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>0.00000000430251107193535</v>
+        <v>2.02392319574642e-213</v>
       </c>
       <c r="B106" t="n">
-        <v>3.8196411699854</v>
+        <v>5.88826313750014</v>
       </c>
       <c r="C106" t="n">
-        <v>0.265</v>
+        <v>0.983</v>
       </c>
       <c r="D106" t="n">
-        <v>0.046</v>
+        <v>0.031</v>
       </c>
       <c r="E106" t="n">
-        <v>0.000157476207743906</v>
+        <v>7.40776128875148e-209</v>
       </c>
       <c r="F106" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G106" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>0.000000000000373931602730906</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000714346082248086</v>
       </c>
       <c r="B107" t="n">
-        <v>3.71732859743612</v>
+        <v>5.53083541423644</v>
       </c>
       <c r="C107" t="n">
-        <v>0.618</v>
+        <v>0.948</v>
       </c>
       <c r="D107" t="n">
-        <v>0.185</v>
+        <v>0.05</v>
       </c>
       <c r="E107" t="n">
-        <v>0.0000000136862705915539</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000261457809563622</v>
       </c>
       <c r="F107" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G107" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>0.000000000000284067251593558</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000546530965785251</v>
       </c>
       <c r="B108" t="n">
-        <v>3.68522498307244</v>
+        <v>3.64521061145247</v>
       </c>
       <c r="C108" t="n">
-        <v>0.353</v>
+        <v>0.431</v>
       </c>
       <c r="D108" t="n">
-        <v>0.056</v>
+        <v>0.025</v>
       </c>
       <c r="E108" t="n">
-        <v>0.0000000103971454755758</v>
+        <v>0.0000000000000000000000000000000000000000000000000000020003579878706</v>
       </c>
       <c r="F108" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G108" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>0.00000000000243020189412211</v>
+        <v>0.00000000000000000000000000000000000000000000411022629945019</v>
       </c>
       <c r="B109" t="n">
-        <v>3.67204099664257</v>
+        <v>3.60935061671039</v>
       </c>
       <c r="C109" t="n">
-        <v>0.324</v>
+        <v>0.966</v>
       </c>
       <c r="D109" t="n">
-        <v>0.05</v>
+        <v>0.266</v>
       </c>
       <c r="E109" t="n">
-        <v>0.0000000889478195267633</v>
+        <v>0.000000000000000000000000000000000000000150438392786176</v>
       </c>
       <c r="F109" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G109" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>0.000000000101878278810466</v>
+        <v>0.0000000000000000000000000000000000140805473974426</v>
       </c>
       <c r="B110" t="n">
-        <v>3.59036836339749</v>
+        <v>3.4424161216296</v>
       </c>
       <c r="C110" t="n">
-        <v>0.353</v>
+        <v>0.31</v>
       </c>
       <c r="D110" t="n">
-        <v>0.07</v>
+        <v>0.022</v>
       </c>
       <c r="E110" t="n">
-        <v>0.00000372884688274186</v>
+        <v>0.000000000000000000000000000000515362115293796</v>
       </c>
       <c r="F110" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G110" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>0.000000000000312127410645698</v>
+        <v>0.0000000000000000000000000000000157348670879461</v>
       </c>
       <c r="B111" t="n">
-        <v>3.5293546659762</v>
+        <v>3.24817427382404</v>
       </c>
       <c r="C111" t="n">
-        <v>0.471</v>
+        <v>0.293</v>
       </c>
       <c r="D111" t="n">
-        <v>0.104</v>
+        <v>0.022</v>
       </c>
       <c r="E111" t="n">
-        <v>0.0000000114241753570432</v>
+        <v>0.000000000000000000000000000575911870285914</v>
       </c>
       <c r="F111" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G111" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>0.000000000091330574609282</v>
+        <v>0.000000000000000000000000000000000532374367317017</v>
       </c>
       <c r="B112" t="n">
-        <v>3.49894458100272</v>
+        <v>2.2813526475598</v>
       </c>
       <c r="C112" t="n">
-        <v>0.676</v>
+        <v>0.983</v>
       </c>
       <c r="D112" t="n">
-        <v>0.286</v>
+        <v>0.39</v>
       </c>
       <c r="E112" t="n">
-        <v>0.00000334279036127433</v>
+        <v>0.0000000000000000000000000000194854342181701</v>
       </c>
       <c r="F112" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G112" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>0.0000000000000000000045933010455393</v>
+        <v>0.000000000000000000206621359244229</v>
       </c>
       <c r="B113" t="n">
-        <v>3.46989738204644</v>
+        <v>2.13485877719515</v>
       </c>
       <c r="C113" t="n">
-        <v>0.647</v>
+        <v>0.448</v>
       </c>
       <c r="D113" t="n">
-        <v>0.134</v>
+        <v>0.085</v>
       </c>
       <c r="E113" t="n">
-        <v>0.000000000000000168119411567784</v>
+        <v>0.00000000000000756254836969804</v>
       </c>
       <c r="F113" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G113" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>0.00000000127571744883481</v>
+        <v>0.000000000000000236102769369858</v>
       </c>
       <c r="B114" t="n">
-        <v>3.45425363497577</v>
+        <v>2.00945673835113</v>
       </c>
       <c r="C114" t="n">
-        <v>0.382</v>
+        <v>0.379</v>
       </c>
       <c r="D114" t="n">
-        <v>0.093</v>
+        <v>0.071</v>
       </c>
       <c r="E114" t="n">
-        <v>0.0000466925343448029</v>
+        <v>0.00000000000864159746170617</v>
       </c>
       <c r="F114" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G114" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>0.000000000207394265826187</v>
+        <v>0.000000000000000000719768629527695</v>
       </c>
       <c r="B115" t="n">
-        <v>3.42002023337974</v>
+        <v>2.00718649150162</v>
       </c>
       <c r="C115" t="n">
-        <v>0.441</v>
+        <v>0.534</v>
       </c>
       <c r="D115" t="n">
-        <v>0.115</v>
+        <v>0.127</v>
       </c>
       <c r="E115" t="n">
-        <v>0.00000759083752350428</v>
+        <v>0.0000000000000263442516093432</v>
       </c>
       <c r="F115" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G115" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>0.00000049116799277924</v>
+        <v>0.0000000000829935954411391</v>
       </c>
       <c r="B116" t="n">
-        <v>3.41023772128507</v>
+        <v>2.00010581964527</v>
       </c>
       <c r="C116" t="n">
-        <v>0.382</v>
+        <v>0.293</v>
       </c>
       <c r="D116" t="n">
-        <v>0.123</v>
+        <v>0.066</v>
       </c>
       <c r="E116" t="n">
-        <v>0.017977239703713</v>
+        <v>0.00000303764858674113</v>
       </c>
       <c r="F116" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G116" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>0.00000000000956808366182299</v>
+        <v>0.00000000000304081866743475</v>
       </c>
       <c r="B117" t="n">
-        <v>3.40060439831691</v>
+        <v>1.96070135956596</v>
       </c>
       <c r="C117" t="n">
-        <v>0.441</v>
+        <v>0.259</v>
       </c>
       <c r="D117" t="n">
-        <v>0.101</v>
+        <v>0.047</v>
       </c>
       <c r="E117" t="n">
-        <v>0.000000350201430106383</v>
+        <v>0.000000111297004046779</v>
       </c>
       <c r="F117" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G117" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>0.0000000025535125836567</v>
+        <v>0.0000000000000463361650271412</v>
       </c>
       <c r="B118" t="n">
-        <v>3.39547318428742</v>
+        <v>1.88952290144537</v>
       </c>
       <c r="C118" t="n">
-        <v>0.382</v>
+        <v>0.483</v>
       </c>
       <c r="D118" t="n">
-        <v>0.093</v>
+        <v>0.129</v>
       </c>
       <c r="E118" t="n">
-        <v>0.0000934611140744189</v>
+        <v>0.0000000016959499761584</v>
       </c>
       <c r="F118" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G118" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>0.000000000170072868791003</v>
+        <v>0.0000000000000761507004844097</v>
       </c>
       <c r="B119" t="n">
-        <v>3.39286180973982</v>
+        <v>1.8880539854604</v>
       </c>
       <c r="C119" t="n">
-        <v>0.294</v>
+        <v>0.379</v>
       </c>
       <c r="D119" t="n">
-        <v>0.05</v>
+        <v>0.083</v>
       </c>
       <c r="E119" t="n">
-        <v>0.0000062248370706195</v>
+        <v>0.00000000278719178842988</v>
       </c>
       <c r="F119" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>0.000000000581956710258148</v>
+        <v>0.000000000045175670847319</v>
       </c>
       <c r="B120" t="n">
-        <v>3.37092085052544</v>
+        <v>1.71153115535115</v>
       </c>
       <c r="C120" t="n">
-        <v>0.294</v>
+        <v>0.517</v>
       </c>
       <c r="D120" t="n">
-        <v>0.052</v>
+        <v>0.182</v>
       </c>
       <c r="E120" t="n">
-        <v>0.0000213001975521585</v>
+        <v>0.00000165347472868272</v>
       </c>
       <c r="F120" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G120" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>0.000000000734297931141309</v>
+        <v>0.000000000183233066865122</v>
       </c>
       <c r="B121" t="n">
-        <v>3.36842970469418</v>
+        <v>1.6229420397126</v>
       </c>
       <c r="C121" t="n">
-        <v>0.324</v>
+        <v>0.5</v>
       </c>
       <c r="D121" t="n">
-        <v>0.063</v>
+        <v>0.159</v>
       </c>
       <c r="E121" t="n">
-        <v>0.000026876038577703</v>
+        <v>0.00000670651348033033</v>
       </c>
       <c r="F121" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G121" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>0.00000000000000000000000000000000906307824071728</v>
+      </c>
+      <c r="B122" t="n">
+        <v>3.72759895958315</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.000000000000000000000000000331717726688493</v>
+      </c>
+      <c r="F122" t="s">
         <v>132</v>
+      </c>
+      <c r="G122" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>0.0000000000000703672050753691</v>
+      </c>
+      <c r="B123" t="n">
+        <v>3.65327577440894</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.00000000257551007296358</v>
+      </c>
+      <c r="F123" t="s">
+        <v>132</v>
+      </c>
+      <c r="G123" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>0.0000000000000000000232261026744345</v>
+      </c>
+      <c r="B124" t="n">
+        <v>3.63327489371761</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.000000000000000850098583986977</v>
+      </c>
+      <c r="F124" t="s">
+        <v>132</v>
+      </c>
+      <c r="G124" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>0.0000000000000377102586114617</v>
+      </c>
+      <c r="B125" t="n">
+        <v>3.3554130859368</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.534</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.00000000138023317543811</v>
+      </c>
+      <c r="F125" t="s">
+        <v>132</v>
+      </c>
+      <c r="G125" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>0.00000000000094978685599034</v>
+      </c>
+      <c r="B126" t="n">
+        <v>3.34525709158439</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.0000000347631487161024</v>
+      </c>
+      <c r="F126" t="s">
+        <v>132</v>
+      </c>
+      <c r="G126" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>0.000000000000969237148923428</v>
+      </c>
+      <c r="B127" t="n">
+        <v>3.33504882141196</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.0000000354750488877464</v>
+      </c>
+      <c r="F127" t="s">
+        <v>132</v>
+      </c>
+      <c r="G127" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>0.000000000118449513833639</v>
+      </c>
+      <c r="B128" t="n">
+        <v>3.28235889207119</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.00000433537065582503</v>
+      </c>
+      <c r="F128" t="s">
+        <v>132</v>
+      </c>
+      <c r="G128" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>0.0000000000000000515786105947015</v>
+      </c>
+      <c r="B129" t="n">
+        <v>3.25279367354934</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.00000000000188782872637667</v>
+      </c>
+      <c r="F129" t="s">
+        <v>132</v>
+      </c>
+      <c r="G129" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>0.000000000000000121121739595737</v>
+      </c>
+      <c r="B130" t="n">
+        <v>3.23909555939276</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.00000000000443317679094358</v>
+      </c>
+      <c r="F130" t="s">
+        <v>132</v>
+      </c>
+      <c r="G130" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>0.000000000000028515376335087</v>
+      </c>
+      <c r="B131" t="n">
+        <v>3.23500185055766</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.00000000104369128924052</v>
+      </c>
+      <c r="F131" t="s">
+        <v>132</v>
+      </c>
+      <c r="G131" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>0.0000000000388270123853657</v>
+      </c>
+      <c r="B132" t="n">
+        <v>3.21139598145166</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.00000142110748031677</v>
+      </c>
+      <c r="F132" t="s">
+        <v>132</v>
+      </c>
+      <c r="G132" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>0.00000000000000141166223756721</v>
+      </c>
+      <c r="B133" t="n">
+        <v>3.20281911219528</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.0000000000516682495571976</v>
+      </c>
+      <c r="F133" t="s">
+        <v>132</v>
+      </c>
+      <c r="G133" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>0.00000000000000000000000000000540250361998013</v>
+      </c>
+      <c r="B134" t="n">
+        <v>3.16620842905931</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.000000000000000000000000197737034994893</v>
+      </c>
+      <c r="F134" t="s">
+        <v>132</v>
+      </c>
+      <c r="G134" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>0.0000000000000000483510356185819</v>
+      </c>
+      <c r="B135" t="n">
+        <v>3.05431999698471</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.00000000000176969625467572</v>
+      </c>
+      <c r="F135" t="s">
+        <v>132</v>
+      </c>
+      <c r="G135" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>0.0000000234187931507521</v>
+      </c>
+      <c r="B136" t="n">
+        <v>3.03345182550259</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.000857151248110677</v>
+      </c>
+      <c r="F136" t="s">
+        <v>132</v>
+      </c>
+      <c r="G136" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>0.000000000177834308306948</v>
+      </c>
+      <c r="B137" t="n">
+        <v>3.02940139938537</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.0000065089135183426</v>
+      </c>
+      <c r="F137" t="s">
+        <v>132</v>
+      </c>
+      <c r="G137" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>0.0000000000223686200142336</v>
+      </c>
+      <c r="B138" t="n">
+        <v>2.99652826080862</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.000000818713861140963</v>
+      </c>
+      <c r="F138" t="s">
+        <v>132</v>
+      </c>
+      <c r="G138" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>0.000000000353431427220835</v>
+      </c>
+      <c r="B139" t="n">
+        <v>2.99294835699499</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.085</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.0000129359436677098</v>
+      </c>
+      <c r="F139" t="s">
+        <v>132</v>
+      </c>
+      <c r="G139" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>0.0000000000000000000792028600488797</v>
+      </c>
+      <c r="B140" t="n">
+        <v>2.97903122619847</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.00000000000000289890388064904</v>
+      </c>
+      <c r="F140" t="s">
+        <v>132</v>
+      </c>
+      <c r="G140" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>0.0000000000000837499868254004</v>
+      </c>
+      <c r="B141" t="n">
+        <v>2.9723488366478</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.00000000306533326779648</v>
+      </c>
+      <c r="F141" t="s">
+        <v>132</v>
+      </c>
+      <c r="G141" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
